--- a/Demo web shop project/Bug_Report.xlsx
+++ b/Demo web shop project/Bug_Report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t xml:space="preserve">Bug ID</t>
   </si>
@@ -55,8 +55,26 @@
     <t xml:space="preserve">Password recovery email not received after using forgot password</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open https://demowebshop.tricentis.com/
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Open https://demowebshop.tricentis.com/
 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2. Click Login                                        3.Click “Forgot Password”                     4. Enter registered email                       5. Click “Recover” button</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">System should send a password recovery email to the registered email address</t>
@@ -69,18 +87,6 @@
   </si>
   <si>
     <t xml:space="preserve">Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Click Login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Click “Forgot Password”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Enter registered email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Click “Recover” button</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open https://demowebshop.tricentis.com/
@@ -97,7 +103,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +125,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -184,7 +196,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -201,23 +213,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -509,7 +521,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="32.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="21.43"/>
@@ -518,11 +530,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="8.43"/>
   </cols>
   <sheetData>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -544,223 +556,215 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I8" s="4" t="s">
+    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G9" s="5"/>
-      <c r="H9" s="6"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G10" s="5"/>
-      <c r="H10" s="6"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="6"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="5"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="5"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="5"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="5"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="5"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="5"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="5"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="5"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="5"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="5"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="5"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="5"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="5"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="5"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G31" s="5"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="5"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G33" s="5"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="5"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="5"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="5"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="5"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="5"/>
+      <c r="G38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="5"/>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="5"/>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="5"/>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="5"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="5"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="5"/>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="5"/>
+      <c r="G45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="5"/>
-      <c r="K46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="K46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K47" s="4"/>
+      <c r="K47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K48" s="7"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K49" s="4"/>
+      <c r="K49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K50" s="4"/>
+      <c r="K50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K51" s="4"/>
+      <c r="K51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K52" s="4"/>
+      <c r="K52" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J74" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K74" s="4" t="s">
+      <c r="K74" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -768,7 +772,7 @@
       <c r="J75" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K75" s="4" t="s">
+      <c r="K75" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -776,15 +780,15 @@
       <c r="J76" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="4" t="s">
-        <v>20</v>
+      <c r="K76" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J77" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K77" s="4" t="s">
+      <c r="K77" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -792,7 +796,7 @@
       <c r="J78" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K78" s="4" t="s">
+      <c r="K78" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -800,7 +804,7 @@
       <c r="J79" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K79" s="4" t="s">
+      <c r="K79" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -808,7 +812,7 @@
       <c r="J80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K80" s="4" t="s">
+      <c r="K80" s="3" t="s">
         <v>15</v>
       </c>
     </row>
